--- a/COCO3_Comp.xlsx
+++ b/COCO3_Comp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\MISTer\CoCo3_Mister\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA23B68B-2ADD-44FC-8659-8DC75A2D5A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A131DB-1291-4F89-9D33-8F93F7182CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13632" yWindow="3240" windowWidth="23856" windowHeight="13092" xr2:uid="{57A7BCA7-2C65-4EF6-A914-7E4BBD33BE36}"/>
+    <workbookView xWindow="18720" yWindow="980" windowWidth="14970" windowHeight="10240" xr2:uid="{57A7BCA7-2C65-4EF6-A914-7E4BBD33BE36}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="48">
   <si>
     <t>Cart</t>
   </si>
@@ -153,13 +153,22 @@
     <t>OS-9 EOU Pipe error</t>
   </si>
   <si>
-    <t>Some garbage on main screen</t>
-  </si>
-  <si>
     <t>Load 20240205</t>
   </si>
   <si>
-    <t>Load 20240216</t>
+    <t>Load 20240318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must set Vido Settings -&gt; LC: = YES </t>
+  </si>
+  <si>
+    <t>Some garbage on main screen [Known  CoCo3 issue]</t>
+  </si>
+  <si>
+    <t>Audio Spectrum Analyzer (1981)</t>
+  </si>
+  <si>
+    <t>Boink</t>
   </si>
 </sst>
 </file>
@@ -185,12 +194,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -205,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -215,6 +230,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,15 +548,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7B1C0CF-A4E7-4A2B-AD36-22ADB22CD812}">
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="14.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="14.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.08984375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,16 +564,16 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -569,7 +587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -583,317 +601,317 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D7" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="2" t="s">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>33</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>32</v>
@@ -905,130 +923,156 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="B30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="37" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="38" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="C38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>42</v>
+      <c r="B39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
